--- a/feedback_forms/030_employee_team_collaboration_feedback_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/030_employee_team_collaboration_feedback_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clear_and_respectful'}</t>
+          <t>clear_and_respectful</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clear and respectful'}</t>
+          <t>Clear and respectful</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'confusing_and_unclear'}</t>
+          <t>confusing_and_unclear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Confusing and unclear'}</t>
+          <t>Confusing and unclear</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unnecessary_gossiping'}</t>
+          <t>unnecessary_gossiping</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unnecessary gossiping'}</t>
+          <t>Unnecessary gossiping</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'meetings_are_very_effective'}</t>
+          <t>meetings_are_very_effective</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Meetings are very effective'}</t>
+          <t>Meetings are very effective</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'meetings_are_somewhat_effective'}</t>
+          <t>meetings_are_somewhat_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Meetings are somewhat effective'}</t>
+          <t>Meetings are somewhat effective</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'meetings_are_not_effective'}</t>
+          <t>meetings_are_not_effective</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Meetings are not effective'}</t>
+          <t>Meetings are not effective</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_very_respectful'}</t>
+          <t>yes,_very_respectful</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, very respectful'}</t>
+          <t>Yes, very respectful</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_respectful'}</t>
+          <t>somewhat_respectful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat respectful'}</t>
+          <t>Somewhat respectful</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_respectful'}</t>
+          <t>not_very_respectful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very respectful'}</t>
+          <t>Not very respectful</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_open_to_change_and_improvement'}</t>
+          <t>yes,_open_to_change_and_improvement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, open to change and improvement'}</t>
+          <t>Yes, open to change and improvement</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_open_to_change_and_improvement'}</t>
+          <t>somewhat_open_to_change_and_improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat open to change and improvement'}</t>
+          <t>Somewhat open to change and improvement</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_open_to_change_and_improvement'}</t>
+          <t>not_open_to_change_and_improvement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not open to change and improvement'}</t>
+          <t>Not open to change and improvement</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_collaboratively'}</t>
+          <t>yes,_collaboratively</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, collaboratively'}</t>
+          <t>Yes, collaboratively</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_collaboratively'}</t>
+          <t>not_collaboratively</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not collaboratively'}</t>
+          <t>Not collaboratively</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'by'}</t>
+          <t>by</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'By'}</t>
+          <t>By</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'by'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'By'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>form_submitted_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'by'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'By'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
